--- a/public/files/AM_Gent_Shift_Premiums_2026.xlsx
+++ b/public/files/AM_Gent_Shift_Premiums_2026.xlsx
@@ -461,7 +461,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated for the SD Worx hackathon demo</t>
+          <t>Generated for the SDWorx hackathon demo</t>
         </is>
       </c>
     </row>
